--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -215,12 +215,6 @@
   </si>
   <si>
     <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE</t>
-  </si>
-  <si>
-    <t>OKREF03249 - {"path": "XWALTZ,XceleraCORE,XceleraSERVICE", "instance": "XceleraSERVICE", "symbol": "enable_ibias", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
@@ -421,12 +415,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog11/CELERAservice.v:166: error: port ``celkelvin_CELG'' is not a port of Xreference.
-1 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -451,6 +439,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
@@ -472,6 +463,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
@@ -490,6 +484,9 @@
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
   </si>
   <si>
@@ -508,16 +505,13 @@
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
 </sst>
 </file>
@@ -883,7 +877,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -948,117 +942,107 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1073,31 +1057,51 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1106,9 +1110,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1118,42 +1122,62 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1163,187 +1187,142 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1358,7 +1337,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1588,6 +1567,31 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1601,254 +1605,264 @@
         <v>120</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>144</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="144">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -368,39 +368,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:100: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:127: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_13ab43f9_d8nsr_nout referenced 1 times.
-        fet_delay_timingskew_13ab43f9_d8nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_0bb48130_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_0bb48130_d1nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_afbafd68_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_afbafd68_d1nsr_pin referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -1177,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1310,34 +1277,19 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1567,6 +1519,31 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1580,49 +1557,24 @@
         <v>117</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>120</v>
-      </c>
-    </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1632,42 +1584,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1677,77 +1629,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -1757,22 +1709,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -1782,52 +1734,52 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -1837,7 +1789,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1852,17 +1804,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="126">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -160,100 +160,7 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -372,26 +279,63 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: Failed to elaborate port expression.
-6 error(s) during elaboration.
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdn_9694dc46.v:52: error: Unknown module type: fet_fetdn_9694dc46_Xfet
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_fetdn_9694dc46_Xfet referenced 1 times.
+***
 </t>
   </si>
   <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -844,137 +788,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>72</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +813,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1009,7 +833,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1024,7 +848,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1039,57 +863,262 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
         <v>78</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1097,204 +1126,74 @@
         <v>82</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>91</v>
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>94</v>
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1519,17 +1418,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1544,37 +1443,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1584,42 +1483,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1629,77 +1528,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -1709,22 +1608,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -1734,62 +1633,62 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1804,17 +1703,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1979,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1989,42 +1888,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="144">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -160,7 +160,100 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -279,63 +372,26 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdn_9694dc46.v:52: error: Unknown module type: fet_fetdn_9694dc46_Xfet
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_fetdn_9694dc46_Xfet referenced 1 times.
-***
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: Failed to elaborate port expression.
+6 error(s) during elaboration.
 </t>
   </si>
   <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER</t>
-  </si>
-  <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -788,12 +844,152 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -806,26 +1002,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A6"/>
@@ -833,7 +1009,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -848,7 +1024,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -863,17 +1039,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -888,12 +1064,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -908,217 +1084,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1126,74 +1097,204 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>86</v>
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>90</v>
+      <c r="A17" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>93</v>
+      <c r="A23" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1418,17 +1519,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1443,37 +1544,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1483,42 +1584,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1528,77 +1629,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -1608,22 +1709,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -1633,62 +1734,62 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1703,17 +1804,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1878,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1888,7 +1989,42 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -9,33 +9,32 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="14" r:id="rId14"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="15" r:id="rId15"/>
-    <sheet name="All Nestos have Verilog File" sheetId="16" r:id="rId16"/>
-    <sheet name="Zero Length Verilog Files" sheetId="17" r:id="rId17"/>
-    <sheet name="Verilog Checker" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency" sheetId="19" r:id="rId19"/>
-    <sheet name="DRM Efficiency Summary" sheetId="20" r:id="rId20"/>
-    <sheet name="DFT Efficiency" sheetId="21" r:id="rId21"/>
-    <sheet name="DFM Efficiency Summary" sheetId="22" r:id="rId22"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
+    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
+    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
+    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
+    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
+    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
+    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
+    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
+    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
+    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
+    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -118,15 +117,6 @@
     <t>XWALTZ,XceleraCORE,XSOFTSTART</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>brick_acf9bbb6.bio</t>
-  </si>
-  <si>
-    <t>brick_acf9bbb6.v</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
@@ -136,7 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>No Shorted Input Nets found.</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -160,100 +153,7 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -371,27 +271,70 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: Failed to elaborate port expression.
-6 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -409,9 +352,6 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
@@ -421,9 +361,6 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
   </si>
   <si>
@@ -445,9 +382,6 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
@@ -463,13 +397,7 @@
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
@@ -844,172 +772,32 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1024,32 +812,52 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1059,42 +867,42 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1109,12 +917,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1124,157 +932,297 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>86</v>
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>110</v>
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1284,17 +1232,22 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1514,67 +1467,42 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>113</v>
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1584,42 +1512,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -1629,77 +1557,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -1709,22 +1637,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -1734,87 +1662,87 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1842,33 +1770,33 @@
         <v>28</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1954,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1967,64 +1895,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>48</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="405">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,10 +126,7 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>No Shorted Input Nets found.</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -141,7 +138,460 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -156,6 +606,420 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -168,9 +1032,6 @@
     <t>D to A Tree</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -178,6 +1039,33 @@
   </si>
   <si>
     <t>Errors</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -274,139 +1162,97 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK</t>
   </si>
   <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+  </si>
+  <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
   </si>
   <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
+    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
   </si>
 </sst>
 </file>
@@ -777,7 +1623,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -797,7 +1643,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -812,7 +1658,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -827,17 +1673,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -847,17 +1693,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -872,17 +1763,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -897,12 +1788,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +1808,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -937,127 +1828,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>368</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -1067,162 +1958,92 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -1237,17 +2058,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -1467,257 +2288,277 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>104</v>
+      <c r="A8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
+      <c r="A11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>85</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>107</v>
+      <c r="A18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
+      <c r="A23" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>111</v>
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>113</v>
+      <c r="A33" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>114</v>
+      <c r="A36" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>116</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>18</v>
+      <c r="A44" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
+      <c r="A47" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
+      <c r="A51" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>117</v>
+      <c r="A53" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
+      <c r="A55" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>101</v>
+      <c r="A58" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>120</v>
+      <c r="A62" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>103</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -1732,17 +2573,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -1777,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1787,17 +2628,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1812,7 +2648,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1822,7 +2658,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1832,12 +2668,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1847,7 +2683,782 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -1862,7 +3473,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1872,7 +3483,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +3498,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1902,17 +3513,787 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="520">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,7 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>No Shorted Input Nets found.</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -138,21 +141,1257 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -165,9 +1404,6 @@
     <t>D to A Tree</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -175,6 +1411,33 @@
   </si>
   <si>
     <t>Errors</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -271,61 +1534,70 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER</t>
   </si>
   <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
   </si>
 </sst>
 </file>
@@ -696,7 +1968,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -716,7 +1988,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -731,7 +2003,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -746,17 +2018,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -766,17 +2038,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -791,17 +2108,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -816,12 +2133,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +2153,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -856,127 +2173,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>58</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>488</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>490</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>71</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>72</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>74</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -986,92 +2303,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1086,17 +2328,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -1316,17 +2558,277 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -1341,17 +2843,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +2888,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1396,12 +2898,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1416,7 +2923,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1426,7 +2933,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1436,12 +2943,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1451,7 +2958,1082 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -1461,22 +4043,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -1486,17 +4098,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -1506,17 +4153,1097 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="171">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,10 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -141,7 +141,142 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -154,6 +289,135 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -274,76 +538,19 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
 </sst>
 </file>
@@ -714,7 +921,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -734,7 +941,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -749,7 +956,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -764,17 +971,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -789,12 +996,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -809,17 +1016,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -834,12 +1041,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +1061,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -874,127 +1081,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1004,162 +1211,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1174,17 +1236,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1471,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1429,17 +1491,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1529,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1545,6 +1607,276 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1559,7 +1891,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1569,7 +1901,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1584,7 +1916,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1599,17 +1931,282 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,10 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -141,142 +141,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -289,135 +154,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -538,19 +274,139 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
     <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
 </sst>
 </file>
@@ -921,7 +777,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -941,7 +797,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -956,7 +812,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -971,17 +827,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -996,12 +852,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1016,17 +872,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1041,12 +897,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1061,7 +917,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1081,127 +937,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>141</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>150</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1211,42 +1067,187 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>167</v>
+  <dimension ref="A1:A47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1466,42 +1467,282 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>167</v>
+  <dimension ref="A1:A68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1591,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1609,289 +1850,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1901,7 +1872,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1916,7 +1887,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1931,282 +1902,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A67"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>127</v>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="231">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,10 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -141,19 +141,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -274,139 +643,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
+    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
 </sst>
 </file>
@@ -777,7 +1101,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -797,7 +1121,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -812,7 +1136,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -827,17 +1151,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -852,12 +1176,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -872,17 +1196,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -897,12 +1221,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +1241,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -937,127 +1261,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1067,162 +1391,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1237,17 +1416,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1467,257 +1646,222 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>78</v>
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>85</v>
+      <c r="A14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>107</v>
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>109</v>
+      <c r="A21" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>110</v>
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>111</v>
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>113</v>
+      <c r="A29" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>88</v>
+      <c r="A32" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>115</v>
+      <c r="A39" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>117</v>
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>118</v>
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>108</v>
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>105</v>
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>110</v>
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>101</v>
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>103</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -1732,17 +1876,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1848,6 +1992,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1857,22 +2321,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1882,17 +2376,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1902,17 +2431,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="231">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,10 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -141,19 +141,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -274,76 +643,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
 </sst>
 </file>
@@ -714,7 +1101,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -734,7 +1121,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -749,7 +1136,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -764,17 +1151,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -789,12 +1176,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -809,17 +1196,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -834,12 +1221,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +1241,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -874,127 +1261,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1004,162 +1391,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1174,17 +1416,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1404,17 +1646,222 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -1429,17 +1876,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1529,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1545,6 +1992,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1554,22 +2321,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1579,17 +2376,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1599,17 +2431,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="238">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -219,6 +219,18 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
+  </si>
+  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -276,22 +288,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -312,22 +324,22 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
@@ -336,22 +348,22 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
@@ -432,6 +444,15 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -492,22 +513,22 @@
     <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -556,6 +577,9 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
+  </si>
+  <si>
+    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -674,9 +698,6 @@
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
@@ -1101,7 +1122,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1121,7 +1142,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1136,7 +1157,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1151,17 +1172,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -1176,12 +1197,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1196,17 +1217,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1216,17 +1237,22 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1267,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1261,127 +1287,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1396,7 +1422,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1416,17 +1442,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1651,32 +1677,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1686,37 +1712,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1726,62 +1752,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1791,17 +1817,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1811,57 +1837,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -1876,17 +1902,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1976,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2136,132 +2162,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
+      <c r="A53" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
+      <c r="A63" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="A68" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2275,43 +2301,63 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2326,47 +2372,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2381,47 +2427,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2431,12 +2477,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2446,22 +2492,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2471,27 +2517,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2501,17 +2547,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2521,252 +2567,272 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
+      <c r="A50" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
+      <c r="A60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
+      <c r="A70" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="221">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -219,18 +219,6 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -312,15 +300,6 @@
     <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -342,9 +321,6 @@
     <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
@@ -366,9 +342,6 @@
     <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
@@ -444,15 +417,6 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -507,12 +471,6 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
     <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -537,15 +495,6 @@
     <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -577,9 +526,6 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
-  </si>
-  <si>
-    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -698,6 +644,9 @@
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
@@ -1122,7 +1071,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1142,7 +1091,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1157,7 +1106,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1172,17 +1121,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1197,12 +1146,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1217,17 +1166,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1237,22 +1186,17 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1267,7 +1211,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1287,127 +1231,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1366,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1442,17 +1386,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1677,32 +1621,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1712,37 +1656,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1752,62 +1696,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1817,17 +1761,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1837,57 +1781,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -1902,17 +1846,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +1946,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2162,132 +2106,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>19</v>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>73</v>
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>77</v>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -2301,63 +2245,28 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2367,52 +2276,47 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2422,52 +2326,47 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2477,12 +2376,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2492,22 +2391,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2517,27 +2416,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2547,17 +2446,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2567,272 +2466,227 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>138</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>16</v>
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>17</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>141</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>18</v>
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>19</v>
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>147</v>
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>151</v>
+      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>26</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
-        <v>83</v>
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -276,22 +276,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -303,43 +303,43 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -471,22 +471,22 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="222">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -607,6 +607,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
+***
 </t>
   </si>
   <si>
@@ -1226,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1352,6 +1361,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1366,7 +1380,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1386,17 +1400,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1621,32 +1635,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1656,37 +1670,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1696,62 +1710,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1761,17 +1775,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1781,47 +1795,47 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -1831,7 +1845,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1846,17 +1860,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="201">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -276,24 +276,9 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
   </si>
   <si>
@@ -303,43 +288,13 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -471,22 +426,7 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -607,15 +547,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -1080,7 +1011,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1100,7 +1031,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1115,7 +1046,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1130,17 +1061,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1155,12 +1086,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1175,17 +1106,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1200,12 +1131,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1151,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1235,137 +1166,132 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1306,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1400,17 +1326,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1635,32 +1561,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1670,37 +1596,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1710,62 +1636,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1775,17 +1701,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1795,57 +1721,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -1860,17 +1786,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1960,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2256,31 +2182,6 @@
     <row r="72" spans="1:1">
       <c r="A72" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2290,12 +2191,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2305,32 +2206,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2340,12 +2216,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2355,32 +2231,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2390,12 +2241,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2405,22 +2256,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2430,27 +2281,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2460,17 +2311,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2480,62 +2331,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -2545,7 +2396,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -2555,12 +2406,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -2570,7 +2421,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2580,42 +2431,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2625,22 +2476,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -2650,12 +2501,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -2665,42 +2516,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="200">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -288,13 +288,10 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -1011,7 +1008,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1031,7 +1028,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1046,7 +1043,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1061,17 +1058,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1086,12 +1083,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1106,17 +1103,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1131,12 +1128,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1151,7 +1148,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1171,127 +1168,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1306,7 +1303,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1326,17 +1323,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1561,32 +1558,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1596,37 +1593,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1636,62 +1633,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1701,17 +1698,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1721,57 +1718,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1786,17 +1783,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2201,7 +2198,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -2216,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2226,12 +2223,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2246,7 +2238,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2256,22 +2248,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2281,27 +2273,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2311,17 +2303,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2331,62 +2323,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -2396,7 +2388,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -2406,12 +2398,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -2421,7 +2413,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2431,42 +2423,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2476,22 +2468,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -2501,12 +2493,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -2516,17 +2508,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="174">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -189,36 +189,6 @@
     <t>Floating pin XU22.i0(49)</t>
   </si>
   <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -273,18 +243,6 @@
     <t>Floating pin XMAIN8.softstart_1ms(35)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -339,36 +297,6 @@
     <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -421,15 +349,6 @@
   </si>
   <si>
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -544,6 +463,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 9 (i2caddr) of SERDEScontrolDFT expects 2 bits, got 8.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 10 (i2cpasswd) of SERDEScontrolDFT expects 2 bits, got 8.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -1008,7 +935,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1028,7 +955,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1043,7 +970,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1058,17 +985,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1083,12 +1010,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1103,17 +1030,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1128,12 +1055,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1075,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1163,132 +1090,137 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1303,7 +1235,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1323,17 +1255,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1558,32 +1490,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1593,37 +1525,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1633,62 +1565,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1698,17 +1630,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1718,57 +1650,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1783,17 +1715,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1992,193 +1924,123 @@
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
+      <c r="A28" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
+      <c r="A31" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
+      <c r="A35" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
+      <c r="A54" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +2055,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2203,7 +2065,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2080,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2233,12 +2095,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2248,22 +2110,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2273,27 +2135,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2303,17 +2165,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2323,202 +2185,132 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>102</v>
+      <c r="A25" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>105</v>
+      <c r="A28" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>109</v>
+      <c r="A32" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>120</v>
+      <c r="A51" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -463,14 +463,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 9 (i2caddr) of SERDEScontrolDFT expects 2 bits, got 8.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 10 (i2cpasswd) of SERDEScontrolDFT expects 2 bits, got 8.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -1090,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1216,11 +1208,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1222,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1255,17 +1242,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1490,32 +1477,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1525,37 +1512,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1565,62 +1552,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1630,17 +1617,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1650,47 +1637,47 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -1700,7 +1687,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1715,17 +1702,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,12 +126,36 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN.CLOCKofftime_0 --&gt; XMAIN.CLOCKofftime_1 --&gt; XMAIN.CLOCKofftime_2 --&gt; XMAIN.CLOCKofftime_3(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input d0 XALGORITHM.enableFAULT --&gt; XALGORITHM.STATEcontrol0 --&gt; XALGORITHM.STATEcontrol1 --&gt; XALGORITHM.STATEcontrol2 --&gt; XALGORITHM.STATEcontrol3(d0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XCONTROL.fcm --&gt; XCONTROL.blank_bottom --&gt; XCONTROL.blank_refresh(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XU21.i0 --&gt; XU22.i0(a0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN.mode_hiccup --&gt; XMAIN.blank_thermal(a0)</t>
+  </si>
+  <si>
     <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
   </si>
   <si>
     <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
+    <t>Shorted input d0 XMAIN.STATEcontrol0 --&gt; XMAIN.STATEcontrol1 --&gt; XMAIN.STATEcontrol2 --&gt; XMAIN.STATEcontrol3(d0)</t>
+  </si>
+  <si>
+    <t>Shorted input a0 XMAIN8.halfway --&gt; XMAIN8.softstart_1ms(a0)</t>
+  </si>
+  <si>
     <t>Shorted Outputs</t>
   </si>
   <si>
@@ -141,106 +165,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -253,102 +178,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -463,6 +292,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173: warning: Port 9 (i2caddr) of SERDEScontrolDFT expects 2 bits, got 4.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173:        : Pruning 2 high bits of the expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173: warning: Port 10 (i2cpasswd) of SERDEScontrolDFT expects 2 bits, got 4.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173:        : Pruning 2 high bits of the expression.
 </t>
   </si>
   <si>
@@ -927,7 +764,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -947,7 +784,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -962,7 +799,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -977,17 +814,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1002,12 +839,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1022,17 +859,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1047,12 +884,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +904,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1082,132 +919,137 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>118</v>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1064,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1242,17 +1084,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1477,32 +1319,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1512,37 +1354,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1552,62 +1394,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1617,17 +1459,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1637,57 +1479,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1702,17 +1544,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1747,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1757,17 +1599,87 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>31</v>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1782,7 +1694,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1792,7 +1704,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1802,12 +1714,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1817,232 +1729,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2052,7 +1754,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2067,7 +1769,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2082,222 +1784,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>104</v>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -165,7 +165,19 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -180,6 +192,15 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -211,6 +232,9 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
+  </si>
+  <si>
+    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -295,14 +319,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173: warning: Port 9 (i2caddr) of SERDEScontrolDFT expects 2 bits, got 4.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173:        : Pruning 2 high bits of the expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173: warning: Port 10 (i2cpasswd) of SERDEScontrolDFT expects 2 bits, got 4.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:173:        : Pruning 2 high bits of the expression.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -337,9 +353,6 @@
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
@@ -764,7 +777,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -784,7 +797,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -799,7 +812,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -814,17 +827,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -839,12 +852,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -859,17 +872,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -879,32 +892,37 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -919,137 +937,132 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>61</v>
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1064,7 +1077,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1084,17 +1097,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1319,32 +1332,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1354,37 +1367,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1394,62 +1407,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1459,17 +1472,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1479,57 +1492,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1544,17 +1557,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1732,6 +1745,26 @@
         <v>43</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1744,7 +1777,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1754,7 +1787,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1769,7 +1802,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1784,17 +1817,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="118">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -165,19 +165,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -192,13 +180,10 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>tdo - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "tdo", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -232,9 +217,6 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
-  </si>
-  <si>
-    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -353,6 +335,9 @@
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
@@ -777,7 +762,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -797,7 +782,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -812,7 +797,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -827,17 +812,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -852,12 +837,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -872,242 +857,237 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1332,32 +1312,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1367,37 +1347,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1407,62 +1387,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1472,17 +1452,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1492,57 +1472,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1557,17 +1537,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1727,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1745,44 +1725,69 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1793,59 +1798,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="116">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -178,12 +178,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdo - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "tdo", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -762,7 +756,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -782,7 +776,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -797,31 +791,51 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -830,9 +844,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -842,42 +856,62 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -887,207 +921,167 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1312,32 +1306,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -1347,37 +1341,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1387,62 +1381,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1452,17 +1446,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1472,82 +1466,82 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>89</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1777,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1787,12 +1781,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="103">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,34 +126,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN.CLOCKofftime_0 --&gt; XMAIN.CLOCKofftime_1 --&gt; XMAIN.CLOCKofftime_2 --&gt; XMAIN.CLOCKofftime_3(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input d0 XALGORITHM.enableFAULT --&gt; XALGORITHM.STATEcontrol0 --&gt; XALGORITHM.STATEcontrol1 --&gt; XALGORITHM.STATEcontrol2 --&gt; XALGORITHM.STATEcontrol3(d0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XCONTROL.fcm --&gt; XCONTROL.blank_bottom --&gt; XCONTROL.blank_refresh(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XU21.i0 --&gt; XU22.i0(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN.mode_hiccup --&gt; XMAIN.blank_thermal(a0)</t>
-  </si>
-  <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
-  </si>
-  <si>
-    <t>Shorted input d0 XMAIN.STATEcontrol0 --&gt; XMAIN.STATEcontrol1 --&gt; XMAIN.STATEcontrol2 --&gt; XMAIN.STATEcontrol3(d0)</t>
-  </si>
-  <si>
-    <t>Shorted input a0 XMAIN8.halfway --&gt; XMAIN8.softstart_1ms(a0)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -295,97 +271,88 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/switchpulldown_92a259b6.v:47: error: Unknown module type: fet_switchpulldown_92a259b6_Xnmos0
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_switchpulldown_92a259b6_Xnmos0 referenced 1 times.
+***
+</t>
+  </si>
+  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
     <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
-    <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
 </sst>
 </file>
@@ -756,7 +723,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -776,7 +743,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -791,7 +758,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -806,17 +773,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -831,12 +798,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -851,17 +818,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -876,12 +843,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +863,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -911,132 +878,137 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>61</v>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1046,42 +1018,187 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
+  <dimension ref="A1:A47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1301,247 +1418,42 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>90</v>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>112</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1586,102 +1498,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1691,7 +1533,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1706,7 +1548,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1716,7 +1558,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1573,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1741,7 +1583,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1598,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1776,7 +1618,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -10,31 +10,30 @@
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
     <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
-    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
-    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
-    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
-    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
-    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
-    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
-    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
-    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
-    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
-    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="12" r:id="rId12"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="13" r:id="rId13"/>
+    <sheet name="All Nestos have Verilog File" sheetId="14" r:id="rId14"/>
+    <sheet name="Zero Length Verilog Files" sheetId="15" r:id="rId15"/>
+    <sheet name="Verilog Checker" sheetId="16" r:id="rId16"/>
+    <sheet name="DRM Efficiency" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency Summary" sheetId="18" r:id="rId18"/>
+    <sheet name="DFT Efficiency" sheetId="19" r:id="rId19"/>
+    <sheet name="DFM Efficiency Summary" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="290">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -123,37 +122,619 @@
     <t>All symbols have nets.</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraRING</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU21</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 19 io: output</t>
+  </si>
+  <si>
+    <t>XU11.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 28 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU46</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 21 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 29 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU47</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 13 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 17 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU48</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 31 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 35 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 39 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 43 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU49</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU50</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 111 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XU29.qb net: 119 io: output</t>
+  </si>
+  <si>
+    <t>XU39.qb net: 121 io: output</t>
+  </si>
+  <si>
+    <t>XU67.qb net: 123 io: output</t>
+  </si>
+  <si>
+    <t>XU23.qb net: 125 io: output</t>
+  </si>
+  <si>
+    <t>XU5.qb net: 127 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU51</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XU14.DRAINk net: 66 io: inout</t>
+  </si>
+  <si>
+    <t>XU5.DRAINk net: 67 io: inout</t>
+  </si>
+  <si>
+    <t>Xfetdriver1.gate_status net: 71 io: output</t>
+  </si>
+  <si>
+    <t>XU16.SOURCEk net: 72 io: inout</t>
+  </si>
+  <si>
+    <t>XU17.ok_cboothv net: 75 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU2</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU26</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU27</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU28</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,XOK</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_sync net: dft_sync io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clock net: dft_clock io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ISLOPECOMP net: ISLOPECOMP io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_synclow net: dft_synclow io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_clock net: fault_clock io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_synchigh net: dft_synchigh io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clocksync net: dft_clocksync io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clockstartup net: dft_clockstartup io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_clockinternal net: dft_clockinternal io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>XOSCEXT.tdi_osc net: noconn_no_dft_tdi_osc1 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.OFF net: XU89_no_dft_noconn_OFF io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.TOP net: XU96_no_dft_noconn_TOP io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.IDLE net: XU93_no_dft_noconn_IDLE io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.FAULT net: XU91_no_dft_noconn_FAULT io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.READY net: XU92_no_dft_noconn_READY io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.BOTTOM net: XU95_no_dft_noconn_BOTTOM io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.POWERUP net: XU90_no_dft_noconn_POWERUP io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.REFRESH net: XU94_no_dft_noconn_REFRESH io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top3SYNC net: XU14_no_dft_noconn_top3SYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top4SYNC net: XU16_no_dft_noconn_top4SYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6aSYNC net: XU18_no_dft_noconn_top6aSYNC io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6bSYNC net: XU20_no_dft_noconn_top6bSYNC io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm0 net: noconn_drm16_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>XU3.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive2 io: output</t>
+  </si>
+  <si>
+    <t>XU9.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive3 io: output</t>
+  </si>
+  <si>
+    <t>XU17.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive4 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswineg net: botswineg io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswipeak net: botswipeak io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.topswipeak net: topswipeak io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswstatus net: botswstatus io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.botswzcross net: botswzcross io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.topswstatus net: topswstatus io: </t>
+  </si>
+  <si>
+    <t>XU22.pulse net: XU12_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>XU22.TAI_ISLOPECOMP net: noconn_no_dft_TAI_ISLOPECOMP6 io: output</t>
+  </si>
+  <si>
+    <t>XU2.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive5 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_run net: fault_run io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_freeze net: fault_freeze io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_delaySHORT net: dft_delaySHORT io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgout net: dft_pgout io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgDELAY net: dft_pgDELAY io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.fault_short net: fault_short io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_REFBUFFER net: dft_REFBUFFER io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgSTARTUP net: dft_pgSTARTUP io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_pgDEGLITCH net: dft_pgDEGLITCH io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.dft_shortdelay net: dft_shortdelay io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>XU4.tdi_padopendrain net: noconn_no_dft_tdi_padopendrain7 io: output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.REFINT net: REFINT io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.go_driver net: go_driver io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.IREF_DRIVER net: IREF_DRIVER io: </t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XU18.pulse net: XU2_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm2 net: noconn_drm48_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm3 net: noconn_drm48_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm4 net: noconn_drm48_drm4_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm5 net: noconn_drm48_drm5_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.OFF net: XU54_no_dft_noconn_OFF io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.RUN net: XU61_no_dft_noconn_RUN io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.FAULT net: XU56_no_dft_noconn_FAULT io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.ENABLE net: XU55_no_dft_noconn_ENABLE io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF4 net: XU58_no_dft_noconn_UNDEF4 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF5 net: XU59_no_dft_noconn_UNDEF5 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.SOFTSTART net: XU57_no_dft_noconn_SOFTSTART io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.REGULATION net: XU60_no_dft_noconn_REGULATION io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.porb net: porb io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.REF0V9 net: REF0V9 io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.go_vcc net: go_vcc io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ok_service net: ok_service io: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.ok_reference net: ok_reference io: </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm1 net: noconn_drm56_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REF net: noconn_no_dft_TAI_REF8 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REFBG net: noconn_no_dft_TAI_REFBG9 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.TAI_VBIAS net: noconn_no_dft_TAI_VBIAS10 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.tdi_vbias net: noconn_no_dft_tdi_vbias11 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XDEBUG.SS net: SS io: </t>
+  </si>
+  <si>
+    <t>XU4.pulse net: XU5_no_dft_noconn_pulse io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE</t>
+  </si>
+  <si>
+    <t>XceleraSERVICE.ok_ibias net: noconn io: output</t>
+  </si>
+  <si>
+    <t>Xoscillator.ok_oscillator net: noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_loadok net: otp_loadok io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_program_done net: otp_program_done io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.unlock net: unlock io: output</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.otp_done net: otp_done io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -271,27 +852,12 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/switchpulldown_92a259b6.v:47: error: Unknown module type: fet_switchpulldown_92a259b6_Xnmos0
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_switchpulldown_92a259b6_Xnmos0 referenced 1 times.
-***
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
@@ -304,18 +870,12 @@
     <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
     <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
     <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
@@ -325,13 +885,7 @@
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
     <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
@@ -718,17 +1272,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -738,27 +1302,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>42</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -768,22 +1327,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>45</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -793,17 +1347,22 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -813,22 +1372,17 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -843,12 +1397,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -858,17 +1412,132 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -878,137 +1547,162 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
+      <c r="A5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>58</v>
+      <c r="A11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>61</v>
+      <c r="A17" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>64</v>
+      <c r="A23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>67</v>
+      <c r="A29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>70</v>
+      <c r="A35" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>73</v>
+      <c r="A41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>77</v>
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -1018,162 +1712,22 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>91</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1183,22 +1737,17 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1418,42 +1967,22 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1498,16 +2027,11 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1518,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1534,6 +2058,16 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1548,12 +2082,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1568,22 +2102,307 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1593,17 +2412,842 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +3262,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="291">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a1 - Shorted inputs (XtieHi.q --&gt; XSERDEScontrolDRMautoNo.a1 --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.enable_hardware)(a1)</t>
   </si>
   <si>
     <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
@@ -1277,7 +1280,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1292,7 +1295,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1307,17 +1310,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -1332,12 +1335,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -1352,17 +1355,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -1377,12 +1380,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -1397,7 +1400,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1417,127 +1420,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -1552,27 +1555,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1582,7 +1585,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -1592,7 +1595,7 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -1602,17 +1605,17 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1622,17 +1625,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -1642,7 +1645,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -1652,7 +1655,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1662,17 +1665,17 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -1682,17 +1685,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1702,7 +1705,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -1717,17 +1720,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1745,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1972,17 +1975,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2017,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2033,6 +2036,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2047,7 +2055,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2057,17 +2065,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2082,17 +2090,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2107,202 +2115,202 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -2312,97 +2320,97 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2417,92 +2425,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -2512,77 +2520,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -2592,27 +2600,27 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -2622,82 +2630,82 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -2707,92 +2715,92 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -2802,82 +2810,82 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -2887,102 +2895,102 @@
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:1">
@@ -2992,182 +3000,182 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -3177,42 +3185,42 @@
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -3222,32 +3230,32 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3262,7 +3270,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/WALTZ/project/Efficiency.xlsx
+++ b/WALTZ/project/Efficiency.xlsx
@@ -13,25 +13,27 @@
     <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
     <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
     <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="7" r:id="rId7"/>
-    <sheet name="Ring Core IO check report" sheetId="8" r:id="rId8"/>
-    <sheet name="D to A Tree" sheetId="9" r:id="rId9"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="10" r:id="rId10"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="11" r:id="rId11"/>
-    <sheet name="All Nestos have Verilog File" sheetId="12" r:id="rId12"/>
-    <sheet name="Zero Length Verilog Files" sheetId="13" r:id="rId13"/>
-    <sheet name="Verilog Checker" sheetId="14" r:id="rId14"/>
-    <sheet name="DRM Efficiency" sheetId="15" r:id="rId15"/>
-    <sheet name="DRM Efficiency Summary" sheetId="16" r:id="rId16"/>
-    <sheet name="DFT Efficiency" sheetId="17" r:id="rId17"/>
-    <sheet name="DFM Efficiency Summary" sheetId="18" r:id="rId18"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="12" r:id="rId12"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="13" r:id="rId13"/>
+    <sheet name="All Nestos have Verilog File" sheetId="14" r:id="rId14"/>
+    <sheet name="Zero Length Verilog Files" sheetId="15" r:id="rId15"/>
+    <sheet name="Verilog Checker" sheetId="16" r:id="rId16"/>
+    <sheet name="DRM Efficiency" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency Summary" sheetId="18" r:id="rId18"/>
+    <sheet name="DFT Efficiency" sheetId="19" r:id="rId19"/>
+    <sheet name="DFM Efficiency Summary" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="290">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -117,49 +119,622 @@
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+    <t>All symbols have nets.</t>
+  </si>
+  <si>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
+  </si>
+  <si>
+    <t>Floating Inputs</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraRING</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU21</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 19 io: output</t>
+  </si>
+  <si>
+    <t>XU11.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 28 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU46</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 21 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 29 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU47</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 13 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 17 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU48</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 31 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 35 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 39 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 43 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU49</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU50</t>
+  </si>
+  <si>
+    <t>XU1.qb net: 111 io: output</t>
+  </si>
+  <si>
+    <t>XU7.qb net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XU13.qb net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XU10.qb net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XU29.qb net: 119 io: output</t>
+  </si>
+  <si>
+    <t>XU39.qb net: 121 io: output</t>
+  </si>
+  <si>
+    <t>XU67.qb net: 123 io: output</t>
+  </si>
+  <si>
+    <t>XU23.qb net: 125 io: output</t>
+  </si>
+  <si>
+    <t>XU5.qb net: 127 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM,XU51</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top3SYNC net: 139 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top4SYNC net: 142 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6aSYNC net: 144 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.top6bSYNC net: 146 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.OFF net: 148 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.POWERUP net: 150 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.FAULT net: 152 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.READY net: 154 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.IDLE net: 156 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.REFRESH net: 158 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.BOTTOM net: 162 io: output</t>
+  </si>
+  <si>
+    <t>XALGORITHM.TOP net: 164 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XU14.DRAINk net: 66 io: inout</t>
+  </si>
+  <si>
+    <t>XU5.DRAINk net: 67 io: inout</t>
+  </si>
+  <si>
+    <t>Xfetdriver1.gate_status net: 71 io: output</t>
+  </si>
+  <si>
+    <t>XU16.SOURCEk net: 72 io: inout</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>XU22.pulse net: 41 io: output</t>
+  </si>
+  <si>
+    <t>XU17.ok_cboothv net: 75 io: output</t>
+  </si>
+  <si>
+    <t>XU18.pulse net: 52 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU2</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU26</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU27</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN,XU28</t>
+  </si>
+  <si>
+    <t>XMAIN.OFF net: 102 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.ENABLE net: 107 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.FAULT net: 110 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.SOFTSTART net: 113 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF4 net: 114 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.UNDEF5 net: 115 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.REGULATION net: 116 io: output</t>
+  </si>
+  <si>
+    <t>XMAIN.RUN net: 117 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,XOK</t>
+  </si>
+  <si>
+    <t>XU12.qb net: 25 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>XU4.pulse net: 24 io: output</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_sync net: dft_sync io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clock net: dft_clock io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ISLOPECOMP net: ISLOPECOMP io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_synclow net: dft_synclow io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_clock net: fault_clock io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_synchigh net: dft_synchigh io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clocksync net: dft_clocksync io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clockstartup net: dft_clockstartup io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_clockinternal net: dft_clockinternal io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>XOSCEXT.tdi_osc net: noconn_no_dft_tdi_osc1 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x02.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x03.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x04.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm0 net: noconn_drm16_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x05.drm1 net: noconn_drm16_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>XU3.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive2 io: output</t>
+  </si>
+  <si>
+    <t>XU9.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive3 io: output</t>
+  </si>
+  <si>
+    <t>XU17.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive4 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswineg net: botswineg io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswipeak net: botswipeak io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.topswipeak net: topswipeak io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswstatus net: botswstatus io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.botswzcross net: botswzcross io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.topswstatus net: topswstatus io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm1 net: noconn_drm24_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x07.drm2 net: noconn_drm24_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>XU22.TAI_ISLOPECOMP net: noconn_no_dft_TAI_ISLOPECOMP6 io: output</t>
+  </si>
+  <si>
+    <t>XU2.tdi_currentlimitlive net: noconn_no_dft_tdi_currentlimitlive5 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_run net: fault_run io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_freeze net: fault_freeze io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_delaySHORT net: dft_delaySHORT io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x08.drm0 net: noconn_drm8L_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x09.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgout net: dft_pgout io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgDELAY net: dft_pgDELAY io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.fault_short net: fault_short io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_REFBUFFER net: dft_REFBUFFER io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgSTARTUP net: dft_pgSTARTUP io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_pgDEGLITCH net: dft_pgDEGLITCH io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_shortdelay net: dft_shortdelay io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>XU4.tdi_padopendrain net: noconn_no_dft_tdi_padopendrain7 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.REFINT net: REFINT io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.go_driver net: go_driver io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.IREF_DRIVER net: IREF_DRIVER io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0A.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm0 net: noconn_drm48_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm2 net: noconn_drm48_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm3 net: noconn_drm48_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm4 net: noconn_drm48_drm4_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0C.drm5 net: noconn_drm48_drm5_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0D.drm0 net: noconn_drm8_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XDEBUG.porb net: porb io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.REF0V9 net: REF0V9 io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.go_vcc net: go_vcc io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ok_service net: ok_service io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.ok_reference net: ok_reference io: input</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm0 net: noconn_drm56_drm0_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm1 net: noconn_drm56_drm1_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm2 net: noconn_drm56_drm2_7 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0E.drm3 net: noconn_drm56_drm3_7 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REF net: noconn_no_dft_TAI_REF8 io: output</t>
+  </si>
+  <si>
+    <t>XU4.TAI_REFBG net: noconn_no_dft_TAI_REFBG9 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.TAI_VBIAS net: noconn_no_dft_TAI_VBIAS10 io: output</t>
+  </si>
+  <si>
+    <t>Xvbias1.tdi_vbias net: noconn_no_dft_tdi_vbias11 io: output</t>
+  </si>
+  <si>
+    <t>XDEBUG.SS net: SS io: input</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_2 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_3 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_4 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_5 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_6 io: output</t>
+  </si>
+  <si>
+    <t>drm_hex0x0F.drm0 net: noconn_drm8_drm0_7 io: output</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE</t>
   </si>
   <si>
-    <t>XceleraSERVICE,TAO</t>
-  </si>
-  <si>
-    <t>Shorted Nets</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>ERROR: Net a1 - Shorted inputs (XtieHi.q --&gt; XSERDEScontrolDRMautoNo.a1 --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.enable_hardware)(a1)</t>
-  </si>
-  <si>
-    <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
-  </si>
-  <si>
-    <t>Floating Inputs</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraRING</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraRING.tmi(tmi[5])</t>
-  </si>
-  <si>
-    <t>Floating pin XNCtmi.noconn(tmi)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDRMautoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDRMautoNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
+    <t>XceleraSERVICE.ok_ibias net: noconn io: output</t>
+  </si>
+  <si>
+    <t>Xoscillator.ok_oscillator net: noconn io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_loadok net: otp_loadok io: output</t>
+  </si>
+  <si>
+    <t>XSERDEScontrolDRMautoNo.otp_program_done net: otp_program_done io: output</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.unlock net: unlock io: output</t>
+  </si>
+  <si>
+    <t>XceleraSERDES.otp_done net: otp_done io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -277,33 +852,12 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/clamp_57e24cde.v:151: error: Unknown module type: feedbackdivider_clamp_57e24cde_FBD
-3 error(s) during elaboration.
-*** These modules were missing:
-        feedbackdivider_clamp_57e24cde_FBD referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:136: warning: Port 1 (noconn) of STONEnoconn expects 1 bits, got 6.
-/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:136:        : Pruning 5 high bits of the expression.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
@@ -316,18 +870,12 @@
     <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
     <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
     <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
@@ -337,13 +885,7 @@
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
     <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
@@ -730,17 +1272,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -755,17 +1307,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -780,12 +1332,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -795,17 +1347,22 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -815,142 +1372,17 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>81</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -960,162 +1392,17 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1125,22 +1412,132 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>103</v>
+      <c r="A5" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1150,17 +1547,162 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -1175,17 +1717,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1403,9 +1965,34 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1421,16 +2008,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1440,27 +2017,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1470,12 +2042,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1485,37 +2057,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1525,42 +2077,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1570,17 +2102,447 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1590,27 +2552,727 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1620,22 +3282,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
